--- a/Engineering_and_Inverse_Analysis/original_BESS.xlsx
+++ b/Engineering_and_Inverse_Analysis/original_BESS.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\工作\项目\科技研发中心\2026\1. 探索Nature\慈溪工程\168离网测试\168离网测试\画图\handle\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="./"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14D055C9-DEBA-4DAD-9050-9099854283A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -51,14 +51,14 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="DengXian"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -92,7 +92,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -153,10 +153,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Hang" typeface="Malgun Gothic"/>
+        <a:font script="Hans" typeface="DengXian Light"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -205,10 +205,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Hang" typeface="Malgun Gothic"/>
+        <a:font script="Hans" typeface="DengXian"/>
+        <a:font script="Hant" typeface="PMingLiU"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
